--- a/analysis/06-if/tables/if_sonnet_5.xlsx
+++ b/analysis/06-if/tables/if_sonnet_5.xlsx
@@ -357,32 +357,32 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Verse</t>
+          <t>verse</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>line</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Sentiment</t>
+          <t>sonnet5_sentiment</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>confidence_score</t>
+          <t>sonnet5_conf</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>reasoning</t>
+          <t>sonnet5_reasoning</t>
         </is>
       </c>
     </row>
@@ -404,11 +404,11 @@
         </is>
       </c>
       <c r="E2">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>calm composure amid surrounding chaos, evoking steady self-assurance</t>
+          <t>This fragment from Kipling's 'If' evokes steady composure and confidence amid chaos, though its incompleteness limits certainty.</t>
         </is>
       </c>
     </row>
@@ -434,7 +434,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>accusatory tone of blame and resentment</t>
+          <t>The phrase suggests blame and accusation, implying resentment or anger directed at someone, though the fragment lacks full context.</t>
         </is>
       </c>
     </row>
@@ -456,11 +456,11 @@
         </is>
       </c>
       <c r="E4">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>emphasizes self-belief and confidence despite others' doubt</t>
+          <t>The line emphasizes self-belief and confidence amid others' doubt, centering on the theme of trust in oneself.</t>
         </is>
       </c>
     </row>
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="E5">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>urging patience and understanding despite others' skepticism</t>
+          <t>The line urges patience and understanding toward others' skepticism, reflecting a trusting, forbearing attitude.</t>
         </is>
       </c>
     </row>
@@ -504,15 +504,15 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Anticipation</t>
+          <t>Trust</t>
         </is>
       </c>
       <c r="E6">
-        <v>0.68</v>
+        <v>0.55</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>reflects patient waiting and expectation</t>
+          <t>The line evokes patient, steadfast endurance suggestive of quiet trust and fortitude rather than a stronger emotion.</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>moral rejection of dishonesty and deceit</t>
+          <t>The line expresses moral rejection of deceit, suggesting distaste toward dishonesty rather than fear or sadness.</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>encourages resilience and moral steadfastness despite adversity</t>
+          <t>The line urges restraint and moral steadiness against hatred, reflecting a value of composed integrity akin to trust in oneself.</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Anticipation</t>
+          <t>Fear</t>
         </is>
       </c>
       <c r="E9">
@@ -590,7 +590,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>cautionary advice suggesting wary, guarded expectation</t>
+          <t>The cautionary tone suggests apprehension about drawing attention or judgment, though the fragment is ambiguous.</t>
         </is>
       </c>
     </row>
@@ -608,15 +608,15 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Anticipation</t>
+          <t>Trust</t>
         </is>
       </c>
       <c r="E10">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>aspirational advice about hope and forward-looking ambition</t>
+          <t>The line offers calm, wise counsel about balancing dreams with control, suggesting a steady, reassuring tone rather than strong emotion.</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Anticipation</t>
+          <t>Trust</t>
         </is>
       </c>
       <c r="E11">
@@ -642,7 +642,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>conditional, forward-looking advice with measured tone</t>
+          <t>The line, from Kipling's 'If—', conveys calm, steady guidance and confident moral counsel rather than a strong emotional pull toward another category.</t>
         </is>
       </c>
     </row>
@@ -660,15 +660,15 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Trust</t>
         </is>
       </c>
       <c r="E12">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>reflective, balanced tone toward opposing outcomes</t>
+          <t>The line, from Kipling's 'If—', conveys steady composure and faith in facing both success and failure equally.</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kipling reference to equanimity and steady resolve toward triumph and disaster</t>
+          <t>The line, from Kipling's 'If—', conveys steady equanimity and composed resilience toward triumph and disaster alike.</t>
         </is>
       </c>
     </row>
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="E14">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>reflective, somber tone about painful honesty</t>
+          <t>The fragmentary line evokes a weary, melancholic tone about confronting painful truth, though it's ambiguous without more context.</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>cynical contempt toward deceit and manipulation</t>
+          <t>The line conveys contempt and cynicism toward deceitful manipulation, suggesting disgust at trickery and folly.</t>
         </is>
       </c>
     </row>
@@ -768,11 +768,11 @@
         </is>
       </c>
       <c r="E16">
-        <v>0.62</v>
+        <v>0.75</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>loss and destruction of life's work evokes grief</t>
+          <t>The line evokes grief and loss over the destruction of one's life's work.</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Anticipation</t>
+          <t>Sadness</t>
         </is>
       </c>
       <c r="E17">
@@ -798,7 +798,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>perseverance and rebuilding despite hardship, suggesting forward-looking resolve</t>
+          <t>The image of stooping and rebuilding with worn-out tools evokes weary perseverance and quiet melancholy.</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>risk-taking gamble evoking tense forward-looking suspense</t>
+          <t>This line from Kipling's 'If' expresses tense forward-looking resolve about risking everything on a single gamble.</t>
         </is>
       </c>
     </row>
@@ -846,11 +846,11 @@
         </is>
       </c>
       <c r="E19">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>gambling metaphor suggesting suspense before a risky outcome</t>
+          <t>The phrase evokes a bold, suspenseful gamble on a single uncertain outcome, emphasizing anticipation of risk.</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>resigned tone about repeated loss and struggle</t>
+          <t>The line evokes weary resignation and loss tied to repeated failure and starting over, characteristic of Kipling's 'If—' reflecting on hardship.</t>
         </is>
       </c>
     </row>
@@ -898,11 +898,11 @@
         </is>
       </c>
       <c r="E21">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>suppressed grief, hidden loss</t>
+          <t>The phrase implies concealed grief over a personal loss, evoking sorrow beneath restraint.</t>
         </is>
       </c>
     </row>
@@ -924,11 +924,11 @@
         </is>
       </c>
       <c r="E22">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>resolute call to persevere toward a future goal</t>
+          <t>The line evokes forward-driven determination and resolve to push through toward a future goal, characteristic of Kipling's 'If—'.</t>
         </is>
       </c>
     </row>
@@ -950,11 +950,11 @@
         </is>
       </c>
       <c r="E23">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>wistful reflection on loss and enduring purpose after absence</t>
+          <t>The phrase evokes loss and enduring absence, suggesting a mournful, wistful tone.</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>expresses weary perseverance amid emotional emptiness</t>
+          <t>The line expresses weary perseverance amid emptiness, evoking a sorrowful, drained emotional state.</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Anticipation</t>
+          <t>Trust</t>
         </is>
       </c>
       <c r="E25">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>exhortation to persevere suggests forward-looking resolve</t>
+          <t>The phrase evokes steadfast resolve and reliance on inner will, suggesting a trust-in-perseverance tone, though the fragment is ambiguous.</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>affirms integrity and steadfast character amid social pressure</t>
+          <t>The line praises maintaining integrity among others, evoking a tone of moral steadiness and trust in one's character.</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>expresses steady, grounded confidence and integrity</t>
+          <t>The line reflects steadfast humility and admirable character, evoking a sense of trust and integrity.</t>
         </is>
       </c>
     </row>
@@ -1080,11 +1080,11 @@
         </is>
       </c>
       <c r="E28">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>fragment suggests resilience and inner steadiness, likely from an inspirational verse</t>
+          <t>The line, echoing Kipling's 'If', evokes resilience and quiet confidence amid adversity.</t>
         </is>
       </c>
     </row>
@@ -1106,11 +1106,11 @@
         </is>
       </c>
       <c r="E29">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>advice on balanced regard for others, calm and measured tone</t>
+          <t>The line, from Kipling's 'If', advises balanced regard and fairness toward all people, reflecting measured trust rather than intense emotion.</t>
         </is>
       </c>
     </row>
@@ -1132,11 +1132,11 @@
         </is>
       </c>
       <c r="E30">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>forward-looking call to seize a fleeting moment</t>
+          <t>The line evokes forward-looking determination and purposeful striving, characteristic of anticipation.</t>
         </is>
       </c>
     </row>
@@ -1158,11 +1158,11 @@
         </is>
       </c>
       <c r="E31">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>reference to time running suggests urgency and forward momentum</t>
+          <t>The line, referencing Kipling's 'If—', evokes a forward-looking sense of striving toward a goal.</t>
         </is>
       </c>
     </row>
@@ -1180,15 +1180,15 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Anticipation</t>
+          <t>Trust</t>
         </is>
       </c>
       <c r="E32">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>triumphant, forward-looking promise of reward</t>
+          <t>The line, echoing Kipling's 'If', conveys an uplifting, reassuring sense of confidence and reward bestowed upon the listener.</t>
         </is>
       </c>
     </row>
@@ -1206,15 +1206,15 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Anticipation</t>
+          <t>Trust</t>
         </is>
       </c>
       <c r="E33">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>proud, forward-looking declaration about future manhood</t>
+          <t>The line, echoing Kipling's 'If—', expresses proud, encouraging affirmation of the son's character, conveying trust and admiration.</t>
         </is>
       </c>
     </row>
